--- a/CSL FETCH/csl_service_start_end.xlsx
+++ b/CSL FETCH/csl_service_start_end.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\demo\capaStudy\CSL FETCH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DF4657-2135-41FB-BA3A-F440F8156D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C153F9D-09D7-47B9-B888-55100142F15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F0A25951-5228-45A8-B859-1B4921BCDC53}"/>
+    <workbookView xWindow="8625" yWindow="-13830" windowWidth="16200" windowHeight="9315" xr2:uid="{F0A25951-5228-45A8-B859-1B4921BCDC53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
   <si>
     <t>QINGDAO</t>
   </si>
@@ -89,10 +89,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AEU8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SERVICE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -129,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>MALTA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SHANGHAI</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -146,6 +138,42 @@
   </si>
   <si>
     <t>JEDDAH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALT1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALT2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHANGHAI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NINGBO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHEKOU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YANTIAN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XIAMEN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AEU9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MALTA FREEPORT</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -199,12 +227,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,26 +571,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48B0069-75D8-4DAD-B162-71688A3CB0F4}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -567,10 +604,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -578,10 +621,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -589,10 +638,16 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -600,10 +655,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -611,10 +672,16 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -622,67 +689,103 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C1:E24">
-    <sortCondition ref="C1:C24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E1:G24">
+    <sortCondition ref="E1:E24"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
